--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_169_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_169_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8625</v>
+        <v>8.1229</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3587</v>
+        <v>7.2158</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5038</v>
+        <v>0.9071</v>
       </c>
       <c r="G2" t="n">
         <v>5.0548</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4216</v>
+        <v>-0.1612</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8215</v>
+        <v>0.0356</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6001</v>
+        <v>-0.1968</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1619</v>
+        <v>5.9655</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3259</v>
+        <v>6.4319</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1639</v>
+        <v>-0.4664</v>
       </c>
       <c r="G3" t="n">
         <v>0.454</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1718</v>
+        <v>-0.0246</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2513</v>
+        <v>-0.1452</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4231</v>
+        <v>0.1206</v>
       </c>
       <c r="V3" t="n">
         <v>3.2166</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>F. NTILIKINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8088</v>
+        <v>4.5477</v>
       </c>
       <c r="E4" t="n">
-        <v>3.954</v>
+        <v>3.88</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8548</v>
+        <v>0.6677</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5614</v>
+        <v>2.0829</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.5438</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6325</v>
+        <v>1.5392</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0165</v>
+        <v>2.97</v>
       </c>
       <c r="K4" t="n">
-        <v>1.17</v>
+        <v>1.9529</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8465</v>
+        <v>1.0171</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4551</v>
+        <v>-0.887</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.241</v>
+        <v>-1.4091</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.214</v>
+        <v>0.5221</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3221</v>
+        <v>-0.3007</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3318</v>
+        <v>0.2322</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0097</v>
+        <v>-0.5329</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3943</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3943</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. NTILIKINA</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5322</v>
+        <v>3.2082</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0662</v>
+        <v>2.4206</v>
       </c>
       <c r="F5" t="n">
-        <v>0.466</v>
+        <v>0.7876</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0829</v>
+        <v>0.5614</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5438</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5392</v>
+        <v>0.6325</v>
       </c>
       <c r="J5" t="n">
-        <v>2.97</v>
+        <v>2.0165</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9529</v>
+        <v>1.17</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0171</v>
+        <v>0.8465</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.887</v>
+        <v>-1.4551</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4091</v>
+        <v>-1.241</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5221</v>
+        <v>-0.214</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3161</v>
+        <v>0.7215</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5816</v>
+        <v>0.7984</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7345</v>
+        <v>-0.0769</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6877</v>
+        <v>3.1585</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8557</v>
+        <v>4.1562</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.168</v>
+        <v>-0.9978</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3467</v>
+        <v>3.1674</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9389</v>
+        <v>1.3973</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5921</v>
+        <v>1.77</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8445</v>
+        <v>5.2232</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6973</v>
+        <v>3.0284</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1472</v>
+        <v>2.1949</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4978</v>
+        <v>-2.0559</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7584</v>
+        <v>-1.631</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.4248</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3589</v>
+        <v>-0.3853</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4208</v>
+        <v>0.1261</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0619</v>
+        <v>-0.5113</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7501</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7501</v>
+        <v>2.2862</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2267</v>
+        <v>2.5242</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2245</v>
+        <v>2.7259</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9978</v>
+        <v>-0.2016</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1674</v>
+        <v>0.3467</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3973</v>
+        <v>0.9389</v>
       </c>
       <c r="I7" t="n">
-        <v>1.77</v>
+        <v>-0.5921</v>
       </c>
       <c r="J7" t="n">
-        <v>5.2232</v>
+        <v>1.8445</v>
       </c>
       <c r="K7" t="n">
-        <v>3.0284</v>
+        <v>1.6973</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1949</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0559</v>
+        <v>-1.4978</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.631</v>
+        <v>-0.7584</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4248</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.317</v>
+        <v>0.1955</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8057</v>
+        <v>0.291</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5113</v>
+        <v>-0.0955</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>1.7501</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2862</v>
+        <v>1.7501</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. NETZIPOGLOU</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3488</v>
+        <v>-0.1763</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3401</v>
+        <v>0.4952</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.6715</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3189</v>
+        <v>0.1573</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6782</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9971</v>
+        <v>0.0936</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2654</v>
+        <v>1.5801</v>
       </c>
       <c r="K8" t="n">
-        <v>0.521</v>
+        <v>0.9579</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7863</v>
+        <v>0.6222</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0535</v>
+        <v>-1.4227</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>-0.8942</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2108</v>
+        <v>-0.5286</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0299</v>
+        <v>-0.282</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0747</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0448</v>
+        <v>-0.3569</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>O. NETZIPOGLOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7997</v>
+        <v>-0.2816</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0946</v>
+        <v>-0.3401</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.0585</v>
       </c>
       <c r="G9" t="n">
+        <v>-0.3189</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6782</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.9971</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.2654</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.7863</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.0535</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.1573</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.06370000000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0936</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.5801</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9579</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.6222</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-1.4227</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.8942</v>
-      </c>
       <c r="O9" t="n">
-        <v>-0.5286</v>
+        <v>-0.2108</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9054</v>
+        <v>0.0373</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5149</v>
+        <v>-0.0747</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3905</v>
+        <v>0.112</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2165</v>
+        <v>-1.1321</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8841</v>
+        <v>-0.7661</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3324</v>
+        <v>-0.366</v>
       </c>
       <c r="G10" t="n">
         <v>0.1284</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1129</v>
+        <v>-0.0286</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7023</v>
+        <v>-1.5514</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2533</v>
+        <v>-1.3713</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4489</v>
+        <v>-0.1801</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1372</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.203</v>
+        <v>0.3539</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0606</v>
+        <v>0.2082</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.799</v>
+        <v>-2.8518</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3429</v>
+        <v>-2.858</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.0062</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3496</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0867</v>
+        <v>1.0339</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3645</v>
+        <v>0.8494</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7222</v>
+        <v>0.1845</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.4135</v>
+        <v>21.5338</v>
       </c>
       <c r="E13" t="n">
-        <v>20.87</v>
+        <v>21.9901</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4562999999999999</v>
+        <v>-0.4563000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>7.1472</v>
@@ -1468,13 +1468,13 @@
         <v>18.5561</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03960000000000008</v>
+        <v>1.1597</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1816</v>
+        <v>2.3019</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.142</v>
+        <v>-1.1421</v>
       </c>
       <c r="V13" t="n">
         <v>5.108499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1708</v>
+        <v>0.7219</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9024</v>
+        <v>1.4306</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7316</v>
+        <v>-0.7087</v>
       </c>
       <c r="G14" t="n">
         <v>0.9489</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0622</v>
+        <v>0.6133</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9085</v>
+        <v>0.4367</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1538</v>
+        <v>0.1766</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2385</v>
+        <v>0.6425</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2106</v>
+        <v>0.4465</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0279</v>
+        <v>0.196</v>
       </c>
       <c r="G15" t="n">
         <v>0.3455</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2693</v>
+        <v>0.1346</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0215</v>
+        <v>0.1896</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0405</v>
+        <v>-0.3214</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0291</v>
+        <v>-0.5009</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0114</v>
+        <v>0.1795</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2303</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1349</v>
+        <v>-0.4158</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4955</v>
+        <v>0.0237</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6304</v>
+        <v>-0.4395</v>
       </c>
       <c r="V16" t="n">
         <v>0.7886</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>A. ATAMNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5314</v>
+        <v>-0.9928</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6362</v>
+        <v>0.8275</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.1677</v>
+        <v>-1.8203</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.731</v>
+        <v>0.5225</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4405</v>
+        <v>-2.4621</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1715</v>
+        <v>2.9846</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6788</v>
+        <v>2.0382</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6923</v>
+        <v>-1.4214</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0134</v>
+        <v>3.4597</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4099</v>
+        <v>-1.5157</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2518</v>
+        <v>-1.0406</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1581</v>
+        <v>-0.4751</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0552</v>
+        <v>0.1652</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9006</v>
+        <v>-0.051</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1546</v>
+        <v>0.2161</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>-2.1444</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ATAMNA</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.599</v>
+        <v>-1.2131</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3557</v>
+        <v>0.4499</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9547</v>
+        <v>-1.6631</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5225</v>
+        <v>-1.1267</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4621</v>
+        <v>-0.8824</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9846</v>
+        <v>-0.2443</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0382</v>
+        <v>0.6109</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4214</v>
+        <v>1.1665</v>
       </c>
       <c r="L18" t="n">
-        <v>3.4597</v>
+        <v>-0.5556</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5157</v>
+        <v>-1.7377</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0406</v>
+        <v>-2.0489</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4751</v>
+        <v>0.3113</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4411</v>
+        <v>-0.174</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>-0.161</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08169999999999999</v>
+        <v>-0.013</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1168</v>
+        <v>-1.2328</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0961</v>
+        <v>2.0465</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2129</v>
+        <v>-3.2793</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1267</v>
+        <v>-0.731</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8824</v>
+        <v>1.4405</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2443</v>
+        <v>-2.1715</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6109</v>
+        <v>2.6788</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1665</v>
+        <v>2.6923</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5556</v>
+        <v>-0.0134</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7377</v>
+        <v>-3.4099</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0489</v>
+        <v>-1.2518</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3113</v>
+        <v>-2.1581</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0776</v>
+        <v>0.3539</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5149</v>
+        <v>0.3108</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5627</v>
+        <v>0.0431</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2642</v>
+        <v>-1.5679</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1004</v>
+        <v>0.5722</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3646</v>
+        <v>-2.1401</v>
       </c>
       <c r="G20" t="n">
         <v>0.0906</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.427</v>
+        <v>0.2693</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>0.0984</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0536</v>
+        <v>0.1709</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4603</v>
+        <v>-2.6455</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6742</v>
+        <v>1.5562</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.1345</v>
+        <v>-4.2017</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6524</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3365</v>
+        <v>0.1513</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1476</v>
+        <v>0.0804</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1444</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7153</v>
+        <v>-4.0013</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4713</v>
+        <v>-3.5892</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.244</v>
+        <v>-0.412</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2862</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6585</v>
+        <v>0.3725</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4696</v>
+        <v>0.3016</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3353</v>
+        <v>-4.0239</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1781</v>
+        <v>-1.3928</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1572</v>
+        <v>-2.6311</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.7672</v>
+        <v>0.7392</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1535</v>
+        <v>0.5149</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6137</v>
+        <v>0.2242</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.847</v>
+        <v>3.5735</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0266</v>
+        <v>1.4522</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8204</v>
+        <v>2.1212</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9202</v>
+        <v>-2.8343</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1269</v>
+        <v>-0.9373</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7933</v>
+        <v>-1.897</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1598</v>
+        <v>-5.5668</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.232</v>
+        <v>-6.0307</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2025</v>
+        <v>-0.2684</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7591</v>
+        <v>-0.0077</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5566</v>
+        <v>-0.2607</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7601</v>
+        <v>-4.2066</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9825</v>
+        <v>-1.532</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7776</v>
+        <v>-2.6747</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7392</v>
+        <v>-4.7672</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5149</v>
+        <v>-1.1535</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2242</v>
+        <v>-3.6137</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5735</v>
+        <v>-1.847</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4522</v>
+        <v>-0.0266</v>
       </c>
       <c r="L24" t="n">
-        <v>2.1212</v>
+        <v>-1.8204</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8343</v>
+        <v>-2.9202</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9373</v>
+        <v>-1.1269</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.897</v>
+        <v>-1.7933</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.5668</v>
+        <v>1.1598</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.0307</v>
+        <v>-0.232</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0047</v>
+        <v>0.3312</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5975</v>
+        <v>0.4052</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4072</v>
+        <v>-0.074</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-20.4136</v>
+        <v>-18.8409</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3146000000000004</v>
+        <v>0.3145</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.7283</v>
+        <v>-19.1555</v>
       </c>
       <c r="G25" t="n">
         <v>-7.1471</v>
@@ -2383,7 +2383,7 @@
         <v>9.997499999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>4.767099999999999</v>
+        <v>4.7671</v>
       </c>
       <c r="M25" t="n">
         <v>-21.9118</v>
@@ -2395,7 +2395,7 @@
         <v>-9.5016</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.1182</v>
+        <v>-8.118199999999998</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.5564</v>
@@ -2404,22 +2404,22 @@
         <v>10.438</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.03969999999999985</v>
+        <v>1.5331</v>
       </c>
       <c r="T25" t="n">
-        <v>1.1421</v>
+        <v>1.142</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1817</v>
+        <v>0.3910999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.108499999999999</v>
+        <v>-5.1085</v>
       </c>
       <c r="W25" t="n">
         <v>2.9641</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.0726</v>
+        <v>-8.072600000000001</v>
       </c>
     </row>
   </sheetData>
